--- a/lab19 IT in progress/labovi/lab1/lab1.xlsx
+++ b/lab19 IT in progress/labovi/lab1/lab1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Korisnik.DESKTOP-JVOQTMK\Documents\GitHub\Computer-Networks-Administration-Lessons\lab19 IT in progress\labovi\lab1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B49FF94-2323-4AB2-A461-CE166FF6EE14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{717D9360-F34D-43B1-A157-3B1CD29A3FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12281,7 +12281,7 @@
       <c r="O424" s="13"/>
       <c r="P424" s="13"/>
       <c r="Q424" s="13"/>
-      <c r="R424" s="13" t="s">
+      <c r="R424" s="20" t="s">
         <v>59</v>
       </c>
       <c r="S424" s="13"/>
@@ -12308,7 +12308,7 @@
       <c r="O425" s="13"/>
       <c r="P425" s="13"/>
       <c r="Q425" s="13"/>
-      <c r="R425" s="13" t="s">
+      <c r="R425" s="20" t="s">
         <v>60</v>
       </c>
       <c r="S425" s="13"/>
@@ -12335,7 +12335,7 @@
       <c r="O426" s="13"/>
       <c r="P426" s="13"/>
       <c r="Q426" s="13"/>
-      <c r="R426" s="13" t="s">
+      <c r="R426" s="20" t="s">
         <v>63</v>
       </c>
       <c r="S426" s="13"/>

--- a/lab19 IT in progress/labovi/lab1/lab1.xlsx
+++ b/lab19 IT in progress/labovi/lab1/lab1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Korisnik.DESKTOP-JVOQTMK\Documents\GitHub\Computer-Networks-Administration-Lessons\lab19 IT in progress\labovi\lab1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{717D9360-F34D-43B1-A157-3B1CD29A3FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B108CA9-CAC6-4560-B294-BC6C2ED10FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1524,6 +1524,50 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>430</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>600772</xdr:colOff>
+      <xdr:row>439</xdr:row>
+      <xdr:rowOff>171704</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9ECD88E-7C1E-1CF0-7055-99156C037F97}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10848975" y="82010250"/>
+          <a:ext cx="4991797" cy="1819529"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -12169,7 +12213,7 @@
       <c r="M420" s="13"/>
       <c r="N420" s="13"/>
       <c r="O420" s="13"/>
-      <c r="P420" s="13" t="s">
+      <c r="P420" s="20" t="s">
         <v>53</v>
       </c>
       <c r="Q420" s="13" t="s">
@@ -12412,7 +12456,7 @@
       <c r="M429" s="13"/>
       <c r="N429" s="13"/>
       <c r="O429" s="13"/>
-      <c r="P429" s="13" t="s">
+      <c r="P429" s="20" t="s">
         <v>55</v>
       </c>
       <c r="Q429" s="13"/>

--- a/lab19 IT in progress/labovi/lab1/lab1.xlsx
+++ b/lab19 IT in progress/labovi/lab1/lab1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Korisnik.DESKTOP-JVOQTMK\Documents\GitHub\Computer-Networks-Administration-Lessons\lab19 IT in progress\labovi\lab1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B108CA9-CAC6-4560-B294-BC6C2ED10FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55B73842-25BE-49EE-907C-A9BEA4024044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
